--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B3FE8BC0-74FD-4404-A3A0-E6B571024271}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF67CA3D-17CD-4C3D-9190-CEC4A98F4B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2295" yWindow="540" windowWidth="19455" windowHeight="12105" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
@@ -53,15 +53,9 @@
     <t>sum([Soil].NO3.kgha)</t>
   </si>
   <si>
-    <t>sum([Soil].Water.MM)asProfileWater</t>
-  </si>
-  <si>
     <t>sum([Soil].Water.MM)</t>
   </si>
   <si>
-    <t>sum([Soil].NO3.kgha)asTotalNO3</t>
-  </si>
-  <si>
     <t>[Wheat].Leaf.CoverGreen</t>
   </si>
   <si>
@@ -132,6 +126,12 @@
   </si>
   <si>
     <t>SimpleLeaf</t>
+  </si>
+  <si>
+    <t>sum([Soil].Water.MM) as ProfileWater</t>
+  </si>
+  <si>
+    <t>sum([Soil].NO3.kgha) as TotalNO3</t>
   </si>
 </sst>
 </file>
@@ -512,10 +512,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -528,18 +528,18 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -552,90 +552,90 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF67CA3D-17CD-4C3D-9190-CEC4A98F4B0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDED6FC4-781D-4268-8E17-0ACBC3371ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2295" yWindow="540" windowWidth="19455" windowHeight="12105" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
+    <workbookView xWindow="-16320" yWindow="-5925" windowWidth="16440" windowHeight="28320" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,91 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
-  <si>
-    <t>[Wheat].Grain.Nconc</t>
-  </si>
-  <si>
-    <t>[Wheat].Grain.NConc</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.MainStemPopulation</t>
-  </si>
-  <si>
-    <t>[Wheat].Population</t>
-  </si>
-  <si>
-    <t>sum([Soil].NO3.kgha)</t>
-  </si>
-  <si>
-    <t>sum([Soil].Water.MM)</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.CoverGreen</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.Canopy.CoverGreen</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.CoverTotal</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.Canopy.CoverTotal</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.Fn</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.FN</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.Fw</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.Canopy.FW</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.Height</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.Canopy.Height</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.LAI</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.Canopy.LAI</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.SpecificAreaCanopy</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.Canopy.SpecificArea</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.Transpiration</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.Canopy.Transpiration</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.StemNumberPerPlant</t>
-  </si>
-  <si>
-    <t>[Wheat].StemNumber</t>
-  </si>
-  <si>
-    <t>[Wheat].Leaf.StemPopulation</t>
-  </si>
-  <si>
-    <t>[Wheat].StemPopulation</t>
-  </si>
-  <si>
-    <t>[Wheat].Root.Depth</t>
-  </si>
-  <si>
-    <t>[Wheat].Root.Network.Depth</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="130">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -128,10 +44,388 @@
     <t>SimpleLeaf</t>
   </si>
   <si>
-    <t>sum([Soil].Water.MM) as ProfileWater</t>
-  </si>
-  <si>
-    <t>sum([Soil].NO3.kgha) as TotalNO3</t>
+    <t>[Phenology].Phyllochron.BasePhyllochron</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Tips</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.SpecificArea</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.HaunStage</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.PTQ</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.Phyllochron</t>
+  </si>
+  <si>
+    <t>Wheat.Arbitrator.DM.TotalFixationSupply</t>
+  </si>
+  <si>
+    <t>Wheat.Arbitrator.DM.TotalPlantDemand</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Live.StructuralWt</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Total.StructuralWt</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Live.StructuralN</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Total.StructuralN</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.MinimumNConc</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.CriticalNConc</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.MaximumNConc</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.DMDemand.Total</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Live.StructuralWt</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Total.StructuralWt</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Live.StructuralN</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Total.StructuralN</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.MinimumNConc</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.CriticalNConc</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.MaximumNConc</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.DMDemand.Total</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Live.StructuralWt</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Total.StructuralWt</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Live.StructuralN</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Total.StructuralN</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.DMDemand.Total</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.DMDemand.Total</t>
+  </si>
+  <si>
+    <t>Wheat.Root.DMDemand.Total</t>
+  </si>
+  <si>
+    <t>[Leaf].Phyllochron.BasePhyllochron</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.MainStemPopulation</t>
+  </si>
+  <si>
+    <t>Wheat.Population</t>
+  </si>
+  <si>
+    <t>sum(Soil.Water.MM)</t>
+  </si>
+  <si>
+    <t>sum(Soil.Water.MM) as ProfileWater</t>
+  </si>
+  <si>
+    <t>sum(Soil.NO3.kgha)</t>
+  </si>
+  <si>
+    <t>sum(Soil.NO3.kgha) as TotalNO3</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Nconc</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.NConc</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.CoverGreen</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Canopy.CoverGreen</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.CoverTotal</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Canopy.CoverTotal</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Fn</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.FN</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Fw</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Canopy.FW</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Height</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Canopy.Height</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.LAI</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Canopy.LAI</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.SpecificAreaCanopy</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Canopy.SpecificArea</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Transpiration</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Canopy.Transpiration</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.StemNumberPerPlant</t>
+  </si>
+  <si>
+    <t>Wheat.StemNumber</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.StemPopulation</t>
+  </si>
+  <si>
+    <t>Wheat.StemPopulation</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Depth</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Network.Depth</t>
+  </si>
+  <si>
+    <t>[Grain].NumberFunction.GrainNumber.GrainsPerGramOfStem</t>
+  </si>
+  <si>
+    <t>[Phenology].PhyllochronPpSensitivity</t>
+  </si>
+  <si>
+    <t>[Leaf].Canopy.GreenExtinctionCoefficient</t>
+  </si>
+  <si>
+    <t>[Leaf].PhyllochronPpSensitivity</t>
+  </si>
+  <si>
+    <t>[Grain].Number.GrainNumber.GrainsPerGramOfStem</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.HaunStage</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Phyllochron</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.MinimumNConc</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.CriticalNConc</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.MaximumNConc</t>
+  </si>
+  <si>
+    <t>Wheat.Arbitrator.Carbon.TotalFixationSupply</t>
+  </si>
+  <si>
+    <t>Wheat.Arbitrator.Carbon.TotalPlantDemand</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Live.Wt.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Live.N.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Total.Wt.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Total.N.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Nitrogen.Concentration.Minimum</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Nitrogen.Concentration.Critical</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Nitrogen.Concentration.Maximum</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Carbon.Demands.Total</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Live.Wt.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Total.Wt.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Live.N.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Total.N.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Nitrogen.Concentration.Minimum</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Nitrogen.Concentration.Critical</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Nitrogen.Concentration.Maximum</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Carbon.Demands.Total</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Live.Wt.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Total.Wt.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Live.N.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Total.N.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Nitrogen.Concentration.Minimum</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Nitrogen.Concentration.Critical</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Nitrogen.Concentration.Maximum</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Carbon.Demands.Total</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Live.StructuralWt</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Live.Wt.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Total.StructuralWt</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Total.Wt.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Live.StructuralN</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Live.N.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Total.StructuralN</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Total.N.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.MinimumNConc</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Nitrogen.Concentration.Minimum</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.CriticalNConc</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Nitrogen.Concentration.Critical</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.MaximumNConc</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Nitrogen.Concentration.Maximum</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Carbon.Demands.Total</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Live.StructuralWt</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Live.Wt.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Total.StructuralWt</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Total.Wt.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Live.StructuralN</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Live.N.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Total.StructuralN</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Total.N.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Root.MinimumNConc</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Nitrogen.Concentration.Minimum</t>
+  </si>
+  <si>
+    <t>Wheat.Root.CriticalNConc</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Nitrogen.Concentration.Critical</t>
+  </si>
+  <si>
+    <t>Wheat.Root.MaximumNConc</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Nitrogen.Concentration.Maximum</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Carbon.Demands.Total</t>
   </si>
 </sst>
 </file>
@@ -503,139 +797,544 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.140625" customWidth="1"/>
+    <col min="1" max="1" width="56.140625" customWidth="1"/>
     <col min="2" max="2" width="87.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="B5" t="s">
-        <v>1</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>23</v>
+      </c>
+      <c r="B41" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B43" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>26</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B44" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>27</v>
+      </c>
+      <c r="B45" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>28</v>
+      </c>
+      <c r="B46" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>29</v>
+      </c>
+      <c r="B47" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>71</v>
+      </c>
+      <c r="B48" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>72</v>
+      </c>
+      <c r="B49" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>73</v>
+      </c>
+      <c r="B50" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>100</v>
+      </c>
+      <c r="B52" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>102</v>
+      </c>
+      <c r="B53" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>104</v>
+      </c>
+      <c r="B54" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>108</v>
+      </c>
+      <c r="B56" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>110</v>
+      </c>
+      <c r="B57" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>112</v>
+      </c>
+      <c r="B58" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>31</v>
+      </c>
+      <c r="B59" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>115</v>
+      </c>
+      <c r="B60" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>117</v>
+      </c>
+      <c r="B61" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>119</v>
+      </c>
+      <c r="B62" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>121</v>
+      </c>
+      <c r="B63" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>123</v>
+      </c>
+      <c r="B64" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>125</v>
+      </c>
+      <c r="B65" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>127</v>
+      </c>
+      <c r="B66" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>32</v>
+      </c>
+      <c r="B67" t="s">
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDED6FC4-781D-4268-8E17-0ACBC3371ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6EB82D-3F87-4907-8E03-778612BDF80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-5925" windowWidth="16440" windowHeight="28320" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="135">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -266,18 +266,6 @@
     <t>Wheat.Arbitrator.Carbon.TotalPlantDemand</t>
   </si>
   <si>
-    <t>Wheat.Stem.Live.Wt.Structural</t>
-  </si>
-  <si>
-    <t>Wheat.Stem.Live.N.Structural</t>
-  </si>
-  <si>
-    <t>Wheat.Stem.Total.Wt.Structural</t>
-  </si>
-  <si>
-    <t>Wheat.Stem.Total.N.Structural</t>
-  </si>
-  <si>
     <t>Wheat.Stem.Nitrogen.Concentration.Minimum</t>
   </si>
   <si>
@@ -290,18 +278,6 @@
     <t>Wheat.Stem.Carbon.Demands.Total</t>
   </si>
   <si>
-    <t>Wheat.Spike.Live.Wt.Structural</t>
-  </si>
-  <si>
-    <t>Wheat.Spike.Total.Wt.Structural</t>
-  </si>
-  <si>
-    <t>Wheat.Spike.Live.N.Structural</t>
-  </si>
-  <si>
-    <t>Wheat.Spike.Total.N.Structural</t>
-  </si>
-  <si>
     <t>Wheat.Spike.Nitrogen.Concentration.Minimum</t>
   </si>
   <si>
@@ -314,18 +290,6 @@
     <t>Wheat.Spike.Carbon.Demands.Total</t>
   </si>
   <si>
-    <t>Wheat.Leaf.Live.Wt.Structural</t>
-  </si>
-  <si>
-    <t>Wheat.Leaf.Total.Wt.Structural</t>
-  </si>
-  <si>
-    <t>Wheat.Leaf.Live.N.Structural</t>
-  </si>
-  <si>
-    <t>Wheat.Leaf.Total.N.Structural</t>
-  </si>
-  <si>
     <t>Wheat.Leaf.Nitrogen.Concentration.Minimum</t>
   </si>
   <si>
@@ -341,27 +305,15 @@
     <t>Wheat.Grain.Live.StructuralWt</t>
   </si>
   <si>
-    <t>Wheat.Grain.Live.Wt.Structural</t>
-  </si>
-  <si>
     <t>Wheat.Grain.Total.StructuralWt</t>
   </si>
   <si>
-    <t>Wheat.Grain.Total.Wt.Structural</t>
-  </si>
-  <si>
     <t>Wheat.Grain.Live.StructuralN</t>
   </si>
   <si>
-    <t>Wheat.Grain.Live.N.Structural</t>
-  </si>
-  <si>
     <t>Wheat.Grain.Total.StructuralN</t>
   </si>
   <si>
-    <t>Wheat.Grain.Total.N.Structural</t>
-  </si>
-  <si>
     <t>Wheat.Grain.MinimumNConc</t>
   </si>
   <si>
@@ -386,27 +338,15 @@
     <t>Wheat.Root.Live.StructuralWt</t>
   </si>
   <si>
-    <t>Wheat.Root.Live.Wt.Structural</t>
-  </si>
-  <si>
     <t>Wheat.Root.Total.StructuralWt</t>
   </si>
   <si>
-    <t>Wheat.Root.Total.Wt.Structural</t>
-  </si>
-  <si>
     <t>Wheat.Root.Live.StructuralN</t>
   </si>
   <si>
-    <t>Wheat.Root.Live.N.Structural</t>
-  </si>
-  <si>
     <t>Wheat.Root.Total.StructuralN</t>
   </si>
   <si>
-    <t>Wheat.Root.Total.N.Structural</t>
-  </si>
-  <si>
     <t>Wheat.Root.MinimumNConc</t>
   </si>
   <si>
@@ -426,6 +366,81 @@
   </si>
   <si>
     <t>Wheat.Root.Carbon.Demands.Total</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.SpecificNitrogen</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Canopy.SpecificNitrogen</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Total.Weight.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Live.Weight.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Live.Weight.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Total.Weight.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Live.Weight.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Total.Weight.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Live.Weight.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Total.Weight.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Live.Weight.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Total.Weight.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Live.Nitrogen.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Total.Nitrogen.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Live.Nitrogen.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Total.Nitrogen.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Live.Nitrogen.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Total.Nitrogen.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Live.Nitrogen.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Total.Nitrogen.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Live.Nitrogen.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Total.Nitrogen.Structural</t>
+  </si>
+  <si>
+    <t>Wheat.Root.WaterUptake</t>
+  </si>
+  <si>
+    <t>Wheat.Root.Network.WaterUptake</t>
+  </si>
+  <si>
+    <t>Wheat.Structure.TotalStemPopn</t>
   </si>
 </sst>
 </file>
@@ -797,7 +812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
-  <dimension ref="A1:B67"/>
+  <dimension ref="A1:B70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.140625" customWidth="1"/>
@@ -934,407 +949,434 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>111</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>62</v>
       </c>
       <c r="B21" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B39" t="s">
-        <v>87</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>131</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B43" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>95</v>
+        <v>122</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="B48" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B49" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="B53" t="s">
-        <v>103</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="B54" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="B55" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="B57" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="B58" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>31</v>
+        <v>96</v>
       </c>
       <c r="B59" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="B60" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="B61" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="B62" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="B63" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="B64" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="B65" t="s">
-        <v>126</v>
+        <v>104</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="B66" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>107</v>
+      </c>
+      <c r="B67" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>32</v>
       </c>
-      <c r="B67" t="s">
-        <v>129</v>
+      <c r="B68" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>132</v>
+      </c>
+      <c r="B69" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>134</v>
+      </c>
+      <c r="B70" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6EB82D-3F87-4907-8E03-778612BDF80F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23734136-5352-4E7B-803A-52E5EB932B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-5925" windowWidth="16440" windowHeight="28320" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="174">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -149,15 +150,9 @@
     <t>sum(Soil.Water.MM)</t>
   </si>
   <si>
-    <t>sum(Soil.Water.MM) as ProfileWater</t>
-  </si>
-  <si>
     <t>sum(Soil.NO3.kgha)</t>
   </si>
   <si>
-    <t>sum(Soil.NO3.kgha) as TotalNO3</t>
-  </si>
-  <si>
     <t>Wheat.Grain.Nconc</t>
   </si>
   <si>
@@ -441,19 +436,147 @@
   </si>
   <si>
     <t>Wheat.Structure.TotalStemPopn</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Moisture</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.Moisture.se</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Dead.NConc</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Height.se</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.HeightError</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.LAIError</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Live.NConc</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Live.Nconc</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.NonStructural.Wt</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.SpecificAreaError</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.StemPopulation.se</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.HaunStageError</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.HaunStageTerminalSpikelet</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.HeadNumber</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.HeadNumber.se</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.HeadNumberError</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.NConc</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.NConc</t>
+  </si>
+  <si>
+    <t>Wheat.Structure.HaunStageFloralInitiation</t>
+  </si>
+  <si>
+    <t>Wheat.Structure.TotalStemPopnError</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.WaterContent</t>
+  </si>
+  <si>
+    <t>Wheat.Grain.WaterContent.se</t>
+  </si>
+  <si>
+    <t>sum([Soil].Water.MM)]</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Dead.Nconc</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Canopy.Height.se</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Canopy.HeightError</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Canopy.LAIError</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Weight.Storage</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Canopy.SpecificAreaError</t>
+  </si>
+  <si>
+    <t>Wheat.StemPopulation.se</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.HaunStageError</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.CAMP.TSHS</t>
+  </si>
+  <si>
+    <t>Wheat.Ear.Number</t>
+  </si>
+  <si>
+    <t>Wheat.Ear.Number.se</t>
+  </si>
+  <si>
+    <t>Wheat.Ear.NumberError</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Nconc</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Nconc</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.CAMP.VSHS</t>
+  </si>
+  <si>
+    <t>Wheat.StemPopulationError</t>
+  </si>
+  <si>
+    <t>TotalNO3</t>
+  </si>
+  <si>
+    <t>ProfileWater</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Var(--jp-code-font-family)"/>
     </font>
   </fonts>
   <fills count="2">
@@ -476,8 +599,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -812,14 +938,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
-  <dimension ref="A1:B70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B90"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="56.140625" customWidth="1"/>
     <col min="2" max="2" width="87.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -827,556 +953,1441 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B10" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B31" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B32" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B33" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B36" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B40" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B41" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B42" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B43" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B46" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B47" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B51" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B53" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B55" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B56" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B57" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B58" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B59" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B60" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B62" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B63" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B64" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B65" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B66" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B67" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B68" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B70" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B71" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B73" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B74" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B75" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B76" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B77" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B79" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B81" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B82" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B83" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B84" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="B85" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B86" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B87" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B88" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>172</v>
+      </c>
+      <c r="B89" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>173</v>
+      </c>
+      <c r="B90" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C94458-8D2F-45A6-90CE-3561672AE312}">
+  <dimension ref="A1:B89"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="79" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="B2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B32" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B35" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B36" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B37" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B40" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B41" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B42" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B43" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B45" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B46" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>110</v>
-      </c>
-      <c r="B17" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+    <row r="49" spans="1:2">
+      <c r="A49" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B49" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B50" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B51" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B21" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>7</v>
-      </c>
-      <c r="B26" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>16</v>
-      </c>
-      <c r="B35" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>17</v>
-      </c>
-      <c r="B36" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>18</v>
-      </c>
-      <c r="B37" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>19</v>
-      </c>
-      <c r="B38" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>20</v>
-      </c>
-      <c r="B39" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>21</v>
-      </c>
-      <c r="B40" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>22</v>
-      </c>
-      <c r="B41" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>23</v>
-      </c>
-      <c r="B42" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>24</v>
-      </c>
-      <c r="B43" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>25</v>
-      </c>
-      <c r="B44" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>26</v>
-      </c>
-      <c r="B45" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>27</v>
-      </c>
-      <c r="B46" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>28</v>
-      </c>
-      <c r="B47" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>29</v>
-      </c>
-      <c r="B48" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>71</v>
-      </c>
-      <c r="B49" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>72</v>
-      </c>
-      <c r="B50" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>73</v>
-      </c>
-      <c r="B51" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>30</v>
+    <row r="52" spans="1:2">
+      <c r="A52" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="B52" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>88</v>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="1" t="s">
+        <v>97</v>
       </c>
       <c r="B53" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>89</v>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="B54" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>90</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="B55" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>91</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="B56" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>92</v>
+    <row r="57" spans="1:2">
+      <c r="A57" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="B57" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>94</v>
+        <v>119</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="1" t="s">
+        <v>130</v>
       </c>
       <c r="B58" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>96</v>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="B59" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>31</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="B60" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>99</v>
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="B61" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>100</v>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="B62" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>101</v>
+        <v>166</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="B63" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B64" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B65" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B66" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B67" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B69" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B70" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B72" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B73" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>102</v>
-      </c>
-      <c r="B64" t="s">
+    <row r="74" spans="1:2">
+      <c r="A74" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B74" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B75" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B76" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B78" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>103</v>
-      </c>
-      <c r="B65" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>105</v>
-      </c>
-      <c r="B66" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>107</v>
-      </c>
-      <c r="B67" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>32</v>
-      </c>
-      <c r="B68" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+    <row r="79" spans="1:2">
+      <c r="A79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B79" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B80" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B69" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>134</v>
-      </c>
-      <c r="B70" t="s">
-        <v>61</v>
+      <c r="B81" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B82" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B83" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B84" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B85" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B86" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B87" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>172</v>
+      </c>
+      <c r="B88" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>173</v>
+      </c>
+      <c r="B89" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23734136-5352-4E7B-803A-52E5EB932B63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C01C7D0-D075-48ED-9154-865740865C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Existing Model renames" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="187">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -559,13 +560,52 @@
   </si>
   <si>
     <t>ProfileWater</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Storage.Wt</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.AnthesisDAS</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.FloweringDAS</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.ReadyForHarvestDAS</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.MaturityDAS</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.NonStructural.Wt</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Storage.Wt</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.NonStructural.Wt</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Storage.Wt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wheat.Structure.HaunStageFloralInitiation: </t>
+  </si>
+  <si>
+    <t>Wheat.SowingData.Population</t>
+  </si>
+  <si>
+    <t>Wheat.SowingData.Population.se</t>
+  </si>
+  <si>
+    <t>Wheat.Population.se</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -578,6 +618,11 @@
       <color theme="1"/>
       <name val="Var(--jp-code-font-family)"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -587,7 +632,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -595,14 +640,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1671,6 +1734,108 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F34CFB7-6746-4EED-A01C-0BEF089865E6}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B11" t="s">
+        <v>186</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C94458-8D2F-45A6-90CE-3561672AE312}">
   <dimension ref="A1:B89"/>
   <sheetFormatPr defaultRowHeight="15"/>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C01C7D0-D075-48ED-9154-865740865C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA3BFE68-6CC6-46CE-84CF-FF8A37335B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="SimpleLeafRenames" sheetId="1" r:id="rId1"/>
     <sheet name="Existing Model renames" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="187">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -624,12 +624,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -659,12 +665,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1001,11 +1011,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
-  <dimension ref="A1:B90"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:B100"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="56.140625" customWidth="1"/>
-    <col min="2" max="2" width="87.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56.109375" customWidth="1"/>
+    <col min="2" max="2" width="87.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1017,714 +1027,794 @@
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>72</v>
+      <c r="A2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
+      <c r="A3" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B4" t="s">
-        <v>93</v>
+      <c r="A4" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s">
-        <v>96</v>
+      <c r="A5" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B6" t="s">
-        <v>122</v>
+      <c r="A6" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" t="s">
-        <v>116</v>
+      <c r="A7" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B8" t="s">
-        <v>95</v>
+      <c r="A8" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" t="s">
-        <v>91</v>
+      <c r="A9" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B10" t="s">
-        <v>153</v>
+      <c r="A10" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B11" t="s">
-        <v>154</v>
+      <c r="A11" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
+      </c>
+      <c r="B12" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>89</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>42</v>
+        <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="B18" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>156</v>
+        <v>90</v>
+      </c>
+      <c r="B19" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>44</v>
+        <v>133</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>46</v>
+        <v>134</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>154</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" t="s">
-        <v>49</v>
+        <v>39</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
-        <v>157</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>158</v>
+        <v>117</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>159</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>140</v>
+        <v>70</v>
+      </c>
+      <c r="B27" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B29" t="s">
-        <v>114</v>
+        <v>135</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="B31" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B33" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="B34" t="s">
-        <v>53</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B36" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B37" t="s">
-        <v>109</v>
+        <v>139</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="B39" t="s">
-        <v>59</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>143</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>162</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>121</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>27</v>
+        <v>141</v>
       </c>
       <c r="B43" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="B45" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B46" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>145</v>
+        <v>108</v>
       </c>
       <c r="B47" t="s">
-        <v>164</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="B48" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="B49" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>103</v>
+        <v>143</v>
       </c>
       <c r="B50" t="s">
-        <v>104</v>
+        <v>162</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="B52" t="s">
-        <v>61</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>118</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>105</v>
+        <v>5</v>
       </c>
       <c r="B55" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
       <c r="B56" t="s">
-        <v>102</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>100</v>
+        <v>145</v>
       </c>
       <c r="B57" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="B58" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>130</v>
+        <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>131</v>
+        <v>68</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="B60" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B61" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>146</v>
+        <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>165</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>147</v>
+        <v>99</v>
       </c>
       <c r="B63" t="s">
-        <v>166</v>
+        <v>124</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="B64" t="s">
-        <v>167</v>
+        <v>118</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="B65" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>18</v>
+        <v>101</v>
       </c>
       <c r="B66" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="B67" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="B68" t="s">
-        <v>78</v>
+        <v>119</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>168</v>
+        <v>130</v>
+      </c>
+      <c r="B69" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B70" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>15</v>
+        <v>146</v>
       </c>
       <c r="B72" t="s">
-        <v>75</v>
+        <v>165</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="B73" t="s">
-        <v>77</v>
+        <v>166</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>12</v>
+        <v>148</v>
       </c>
       <c r="B74" t="s">
-        <v>126</v>
+        <v>167</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B75" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B77" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>169</v>
+        <v>22</v>
+      </c>
+      <c r="B78" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B79" t="s">
-        <v>127</v>
+        <v>149</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B80" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="1" t="s">
-        <v>151</v>
+        <v>19</v>
       </c>
       <c r="B81" t="s">
-        <v>170</v>
+        <v>113</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="1" t="s">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="B82" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="1" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>77</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="1" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="1" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="B85" t="s">
-        <v>64</v>
+        <v>111</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="1" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B86" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="1" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="B87" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B89" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B90" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B91" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B92" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B93" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B94" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B95" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B96" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B97" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B98" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
-      <c r="A89" t="s">
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
         <v>172</v>
       </c>
-      <c r="B89" t="s">
+      <c r="B99" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
-      <c r="A90" t="s">
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
         <v>173</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B100" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1736,10 +1826,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F34CFB7-6746-4EED-A01C-0BEF089865E6}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1838,7 +1928,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C94458-8D2F-45A6-90CE-3561672AE312}">
   <dimension ref="A1:B89"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="79" bestFit="1" customWidth="1"/>
   </cols>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA3BFE68-6CC6-46CE-84CF-FF8A37335B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743CED89-89BC-4A02-B161-5D885986D717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
+    <workbookView xWindow="-16320" yWindow="-5925" windowWidth="16440" windowHeight="28320" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
   <sheets>
     <sheet name="SimpleLeafRenames" sheetId="1" r:id="rId1"/>
@@ -1012,10 +1012,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
   <dimension ref="A1:B100"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="56.109375" customWidth="1"/>
-    <col min="2" max="2" width="87.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56.140625" customWidth="1"/>
+    <col min="2" max="2" width="87.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1084,7 +1084,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>170</v>
@@ -1826,10 +1826,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F34CFB7-6746-4EED-A01C-0BEF089865E6}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="42.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1928,7 +1928,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C94458-8D2F-45A6-90CE-3561672AE312}">
   <dimension ref="A1:B89"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="79" bestFit="1" customWidth="1"/>
   </cols>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{743CED89-89BC-4A02-B161-5D885986D717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43F092F-CA83-4F43-8B6B-A587E13242CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-5925" windowWidth="16440" windowHeight="28320" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
+    <workbookView xWindow="2064" yWindow="816" windowWidth="17280" windowHeight="11616" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
   <sheets>
     <sheet name="SimpleLeafRenames" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="192">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -599,6 +599,21 @@
   </si>
   <si>
     <t>Wheat.Population.se</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Live.StorageWt</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Live.Weight.Storage</t>
+  </si>
+  <si>
+    <t>Wheat.Spike.Live.StorageWt</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Live.StorageWt</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Live.Storage.Wt</t>
   </si>
 </sst>
 </file>
@@ -1011,11 +1026,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
-  <dimension ref="A1:B100"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:B103"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="56.140625" customWidth="1"/>
-    <col min="2" max="2" width="87.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56.109375" customWidth="1"/>
+    <col min="2" max="2" width="87.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1420,401 +1435,425 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>3</v>
+        <v>187</v>
       </c>
       <c r="B51" t="s">
-        <v>67</v>
+        <v>188</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B53" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>144</v>
+        <v>5</v>
       </c>
       <c r="B56" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B57" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>6</v>
+        <v>145</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>164</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="B61" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="B62" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B64" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B65" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B66" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B67" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B68" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="B69" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>23</v>
+        <v>130</v>
       </c>
       <c r="B70" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B71" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>146</v>
+        <v>25</v>
       </c>
       <c r="B72" t="s">
-        <v>165</v>
+        <v>81</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B73" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B74" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="B75" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B76" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B77" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>168</v>
+        <v>22</v>
+      </c>
+      <c r="B79" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B80" t="s">
-        <v>129</v>
+        <v>149</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B81" t="s">
-        <v>113</v>
+        <v>189</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B82" t="s">
-        <v>75</v>
+        <v>129</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B83" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B84" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B86" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B87" t="s">
-        <v>74</v>
+        <v>111</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>169</v>
+        <v>16</v>
+      </c>
+      <c r="B88" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B89" t="s">
-        <v>127</v>
+        <v>74</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B90" t="s">
-        <v>110</v>
+        <v>150</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="B91" t="s">
-        <v>170</v>
+        <v>190</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="1" t="s">
-        <v>132</v>
+        <v>13</v>
       </c>
       <c r="B92" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="1" t="s">
-        <v>152</v>
+        <v>11</v>
       </c>
       <c r="B93" t="s">
-        <v>171</v>
+        <v>110</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="1" t="s">
-        <v>62</v>
+        <v>151</v>
       </c>
       <c r="B94" t="s">
-        <v>66</v>
+        <v>170</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="1" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="B95" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="1" t="s">
-        <v>2</v>
+        <v>152</v>
       </c>
       <c r="B96" t="s">
-        <v>33</v>
+        <v>171</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B97" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B98" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B99" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B100" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B101" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
-      <c r="A99" t="s">
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
         <v>172</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B102" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
-      <c r="A100" t="s">
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
         <v>173</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B103" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1826,10 +1865,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F34CFB7-6746-4EED-A01C-0BEF089865E6}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.140625" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.109375" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1928,7 +1967,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C94458-8D2F-45A6-90CE-3561672AE312}">
   <dimension ref="A1:B89"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="79" bestFit="1" customWidth="1"/>
   </cols>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43F092F-CA83-4F43-8B6B-A587E13242CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEEAA140-925C-4C18-9F96-55A1AE2E4FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2064" yWindow="816" windowWidth="17280" windowHeight="11616" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
   <sheets>
     <sheet name="SimpleLeafRenames" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="190">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -562,9 +562,6 @@
     <t>ProfileWater</t>
   </si>
   <si>
-    <t>Wheat.Leaf.Storage.Wt</t>
-  </si>
-  <si>
     <t>Wheat.Phenology.AnthesisDAS</t>
   </si>
   <si>
@@ -580,15 +577,9 @@
     <t>Wheat.Spike.NonStructural.Wt</t>
   </si>
   <si>
-    <t>Wheat.Spike.Storage.Wt</t>
-  </si>
-  <si>
     <t>Wheat.Stem.NonStructural.Wt</t>
   </si>
   <si>
-    <t>Wheat.Stem.Storage.Wt</t>
-  </si>
-  <si>
     <t xml:space="preserve">Wheat.Structure.HaunStageFloralInitiation: </t>
   </si>
   <si>
@@ -613,7 +604,10 @@
     <t>Wheat.Stem.Live.StorageWt</t>
   </si>
   <si>
-    <t>Wheat.Stem.Live.Storage.Wt</t>
+    <t>Wheat.Spike.Live.Weight.Storage</t>
+  </si>
+  <si>
+    <t>Wheat.Stem.Live.Weight.Storage</t>
   </si>
 </sst>
 </file>
@@ -1054,15 +1048,15 @@
         <v>141</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1075,26 +1069,26 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1107,7 +1101,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="4" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>35</v>
@@ -1115,10 +1109,10 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="4" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1347,34 +1341,34 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>34</v>
+        <v>184</v>
       </c>
       <c r="B40" t="s">
-        <v>35</v>
+        <v>185</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="B41" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>141</v>
+        <v>69</v>
       </c>
       <c r="B43" t="s">
-        <v>160</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1435,10 +1429,10 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B51" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1675,10 +1669,10 @@
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1755,10 +1749,10 @@
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1892,15 +1886,15 @@
         <v>141</v>
       </c>
       <c r="B3" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" t="s">
         <v>175</v>
-      </c>
-      <c r="B4" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1913,31 +1907,31 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" t="s">
         <v>177</v>
-      </c>
-      <c r="B6" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B7" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B8" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B9" t="s">
         <v>170</v>
@@ -1945,7 +1939,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B10" t="s">
         <v>35</v>
@@ -1953,10 +1947,10 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B11" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEEAA140-925C-4C18-9F96-55A1AE2E4FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD8FCC7-85A4-4F1D-B97F-B95BB6444D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
+    <workbookView xWindow="-16320" yWindow="-5925" windowWidth="16440" windowHeight="28320" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
   <sheets>
     <sheet name="SimpleLeafRenames" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="192">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -608,6 +608,12 @@
   </si>
   <si>
     <t>Wheat.Stem.Live.Weight.Storage</t>
+  </si>
+  <si>
+    <t>(Wheat.Leaf.Transpiration+ISoilWater.Es+MicroClimate.PrecipitationInterception)</t>
+  </si>
+  <si>
+    <t>(Wheat.Leaf.Transpiration + ISoilWater.Es + MicroClimate.PrecipitationInterception)</t>
   </si>
 </sst>
 </file>
@@ -1020,11 +1026,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
-  <dimension ref="A1:B103"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:B104"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="56.109375" customWidth="1"/>
-    <col min="2" max="2" width="87.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56.140625" customWidth="1"/>
+    <col min="2" max="2" width="87.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1849,6 +1855,14 @@
       </c>
       <c r="B103" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>190</v>
+      </c>
+      <c r="B104" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -1859,10 +1873,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F34CFB7-6746-4EED-A01C-0BEF089865E6}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.109375" customWidth="1"/>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1961,7 +1975,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C94458-8D2F-45A6-90CE-3561672AE312}">
   <dimension ref="A1:B89"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="79" bestFit="1" customWidth="1"/>
   </cols>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD8FCC7-85A4-4F1D-B97F-B95BB6444D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FC5128-BD09-426B-8BE9-80AA61BCDE75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-5925" windowWidth="16440" windowHeight="28320" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
   <sheets>
     <sheet name="SimpleLeafRenames" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="192">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -1026,11 +1026,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
-  <dimension ref="A1:B104"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:B99"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="56.140625" customWidth="1"/>
-    <col min="2" max="2" width="87.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56.109375" customWidth="1"/>
+    <col min="2" max="2" width="87.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1203,279 +1203,279 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>38</v>
+        <v>89</v>
+      </c>
+      <c r="B22" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="B24" t="s">
-        <v>117</v>
+        <v>41</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B28" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>156</v>
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>46</v>
+        <v>136</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="B32" t="s">
-        <v>49</v>
+        <v>158</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>136</v>
+        <v>50</v>
       </c>
       <c r="B33" t="s">
-        <v>157</v>
+        <v>51</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B34" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>138</v>
+        <v>26</v>
       </c>
       <c r="B36" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>140</v>
+        <v>184</v>
+      </c>
+      <c r="B37" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>120</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="B39" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>184</v>
+        <v>69</v>
       </c>
       <c r="B40" t="s">
-        <v>185</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="B41" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="B42" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="B43" t="s">
-        <v>82</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>109</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>142</v>
+        <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>161</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>108</v>
+        <v>143</v>
       </c>
       <c r="B47" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>56</v>
+        <v>184</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>185</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>143</v>
+        <v>29</v>
       </c>
       <c r="B50" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>184</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
-        <v>185</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="B52" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="B53" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>27</v>
+        <v>144</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>54</v>
+        <v>145</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B56" t="s">
         <v>67</v>
@@ -1483,385 +1483,345 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>144</v>
+        <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>163</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="B58" t="s">
-        <v>164</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B61" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="B62" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
       <c r="B63" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B64" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B65" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B66" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
       <c r="B67" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="B68" t="s">
-        <v>125</v>
+        <v>79</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="B70" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>23</v>
+        <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>166</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>25</v>
+        <v>148</v>
       </c>
       <c r="B72" t="s">
-        <v>81</v>
+        <v>167</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="B73" t="s">
-        <v>165</v>
+        <v>128</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>147</v>
+        <v>18</v>
       </c>
       <c r="B74" t="s">
-        <v>166</v>
+        <v>112</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>148</v>
+        <v>24</v>
       </c>
       <c r="B75" t="s">
-        <v>167</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B76" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B77" t="s">
-        <v>112</v>
+        <v>186</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B78" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B79" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="B80" s="1" t="s">
-        <v>168</v>
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>188</v>
+        <v>17</v>
+      </c>
+      <c r="B81" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="1" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B84" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B85" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B86" t="s">
-        <v>126</v>
+        <v>187</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B87" t="s">
-        <v>111</v>
+        <v>127</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="1" t="s">
-        <v>14</v>
+        <v>151</v>
       </c>
       <c r="B89" t="s">
-        <v>74</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>169</v>
+        <v>132</v>
+      </c>
+      <c r="B90" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>189</v>
+        <v>152</v>
+      </c>
+      <c r="B91" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="1" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="B92" t="s">
-        <v>127</v>
+        <v>66</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="1" t="s">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="B93" t="s">
-        <v>110</v>
+        <v>64</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="1" t="s">
-        <v>151</v>
+        <v>2</v>
       </c>
       <c r="B94" t="s">
-        <v>170</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="1" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
       <c r="B95" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B96" t="s">
-        <v>171</v>
+        <v>36</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="1" t="s">
-        <v>62</v>
+      <c r="A97" t="s">
+        <v>172</v>
       </c>
       <c r="B97" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
     </row>
     <row r="98" spans="1:2">
-      <c r="A98" s="1" t="s">
-        <v>64</v>
+      <c r="A98" t="s">
+        <v>173</v>
       </c>
       <c r="B98" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="99" spans="1:2">
-      <c r="A99" s="1" t="s">
-        <v>2</v>
+      <c r="A99" t="s">
+        <v>190</v>
       </c>
       <c r="B99" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B100" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B101" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" t="s">
-        <v>172</v>
-      </c>
-      <c r="B102" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" t="s">
-        <v>173</v>
-      </c>
-      <c r="B103" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" t="s">
-        <v>190</v>
-      </c>
-      <c r="B104" t="s">
         <v>191</v>
       </c>
     </row>
@@ -1873,10 +1833,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F34CFB7-6746-4EED-A01C-0BEF089865E6}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.140625" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.109375" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1975,7 +1935,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C94458-8D2F-45A6-90CE-3561672AE312}">
   <dimension ref="A1:B89"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="79" bestFit="1" customWidth="1"/>
   </cols>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23FC5128-BD09-426B-8BE9-80AA61BCDE75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24550676-F1E5-4E64-922C-DBF3FDF28876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
   <sheets>
     <sheet name="SimpleLeafRenames" sheetId="1" r:id="rId1"/>
-    <sheet name="Existing Model renames" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="MaxLeafSizeRenames" sheetId="4" r:id="rId2"/>
+    <sheet name="Existing Model renames" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="196">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -614,6 +615,18 @@
   </si>
   <si>
     <t>(Wheat.Leaf.Transpiration + ISoilWater.Es + MicroClimate.PrecipitationInterception)</t>
+  </si>
+  <si>
+    <t>MaxLeafSize.Script.LeafPosition</t>
+  </si>
+  <si>
+    <t>MaxLeafSize.Script.MaxLeafSize</t>
+  </si>
+  <si>
+    <t>OutputMaxLeafSize.Script.LeafPosition</t>
+  </si>
+  <si>
+    <t>OutputMaxLeafSize.Script.MaxLeafSize</t>
   </si>
 </sst>
 </file>
@@ -1026,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
-  <dimension ref="A1:B99"/>
+  <dimension ref="A1:B101"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="56.109375" customWidth="1"/>
@@ -1355,7 +1368,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="B41" t="s">
         <v>53</v>
@@ -1363,7 +1376,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>53</v>
@@ -1823,6 +1836,22 @@
       </c>
       <c r="B99" t="s">
         <v>191</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>192</v>
+      </c>
+      <c r="B100" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>193</v>
+      </c>
+      <c r="B101" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -1831,6 +1860,40 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B7E1F01-A2F7-45A9-995C-5EC6E55D65FA}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" t="s">
+        <v>195</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F34CFB7-6746-4EED-A01C-0BEF089865E6}">
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1932,7 +1995,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C94458-8D2F-45A6-90CE-3561672AE312}">
   <dimension ref="A1:B89"/>
   <sheetFormatPr defaultRowHeight="14.4"/>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24550676-F1E5-4E64-922C-DBF3FDF28876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498D0999-C436-4324-AB37-67024CD1B660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
+    <workbookView xWindow="-16320" yWindow="-5925" windowWidth="16440" windowHeight="28320" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
   <sheets>
     <sheet name="SimpleLeafRenames" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="197">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -627,6 +627,9 @@
   </si>
   <si>
     <t>OutputMaxLeafSize.Script.MaxLeafSize</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.SpecificAreaTotal</t>
   </si>
 </sst>
 </file>
@@ -1379,7 +1382,7 @@
         <v>4</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
+        <v>196</v>
       </c>
     </row>
     <row r="43" spans="1:2">

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{498D0999-C436-4324-AB37-67024CD1B660}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07ADDC4-4F46-43F7-B5A8-39AC61C4EFFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-5925" windowWidth="16440" windowHeight="28320" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
   <sheets>
     <sheet name="SimpleLeafRenames" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="199">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -629,7 +629,13 @@
     <t>OutputMaxLeafSize.Script.MaxLeafSize</t>
   </si>
   <si>
-    <t>Wheat.Leaf.SpecificAreaTotal</t>
+    <t>Wheat.Leaf.Canopy.GreenSpecificArea</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Canopy.TotalSpecificArea</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.TotalSpecificArea</t>
   </si>
 </sst>
 </file>
@@ -1371,15 +1377,15 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>52</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>197</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="B42" t="s">
         <v>196</v>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07ADDC4-4F46-43F7-B5A8-39AC61C4EFFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC9778A-2E83-47CF-ACB4-9A36829CD766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
   <sheets>
     <sheet name="SimpleLeafRenames" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="200">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -635,7 +635,10 @@
     <t>Wheat.Leaf.Canopy.TotalSpecificArea</t>
   </si>
   <si>
-    <t>Wheat.Leaf.TotalSpecificArea</t>
+    <t>//Wheat.Leaf.Canopy.TotalSpecificArea</t>
+  </si>
+  <si>
+    <t>Wheat.Leaf.Canopy.GreenSpecificNitrogen</t>
   </si>
 </sst>
 </file>
@@ -1048,7 +1051,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
-  <dimension ref="A1:B101"/>
+  <dimension ref="A1:B102"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="56.109375" customWidth="1"/>
@@ -1393,473 +1396,481 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>142</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
-        <v>161</v>
+        <v>196</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="B44" t="s">
-        <v>109</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>199</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>143</v>
+        <v>58</v>
       </c>
       <c r="B47" t="s">
-        <v>162</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>184</v>
+        <v>143</v>
       </c>
       <c r="B48" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>3</v>
+        <v>184</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>185</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>121</v>
+        <v>67</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B51" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>144</v>
+        <v>5</v>
       </c>
       <c r="B54" t="s">
-        <v>163</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B55" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>6</v>
+        <v>145</v>
       </c>
       <c r="B56" t="s">
-        <v>67</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>104</v>
+        <v>68</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="B59" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="B60" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>124</v>
+        <v>61</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B62" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B63" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B64" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B65" t="s">
-        <v>125</v>
+        <v>102</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B66" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="B67" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>23</v>
+        <v>130</v>
       </c>
       <c r="B68" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B69" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>146</v>
+        <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>165</v>
+        <v>81</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B71" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B72" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="B73" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B74" t="s">
-        <v>112</v>
+        <v>128</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B75" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B76" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>188</v>
+        <v>22</v>
+      </c>
+      <c r="B77" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B78" t="s">
-        <v>129</v>
+        <v>186</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B79" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B80" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B81" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>111</v>
+        <v>126</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B84" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B85" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B86" s="1" t="s">
-        <v>189</v>
+        <v>14</v>
+      </c>
+      <c r="B86" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B87" t="s">
-        <v>127</v>
+        <v>187</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B88" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="1" t="s">
-        <v>151</v>
+        <v>11</v>
       </c>
       <c r="B89" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="1" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="B90" t="s">
-        <v>59</v>
+        <v>170</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="1" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="B91" t="s">
-        <v>171</v>
+        <v>59</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="1" t="s">
-        <v>62</v>
+        <v>152</v>
       </c>
       <c r="B92" t="s">
-        <v>66</v>
+        <v>171</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B93" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="1" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="B94" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="1" t="s">
-        <v>63</v>
+        <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B96" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B97" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" t="s">
-        <v>172</v>
-      </c>
-      <c r="B97" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B98" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="B99" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B100" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
+        <v>192</v>
+      </c>
+      <c r="B101" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
         <v>193</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B102" t="s">
         <v>195</v>
       </c>
     </row>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC9778A-2E83-47CF-ACB4-9A36829CD766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C27339A-679B-4FC3-92AB-EA1ADCC2F12E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="200">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -705,7 +705,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -716,6 +716,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1051,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
-  <dimension ref="A1:B102"/>
+  <dimension ref="A1:B99"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="56.109375" customWidth="1"/>
@@ -1212,183 +1216,183 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="B21" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>48</v>
+        <v>136</v>
       </c>
       <c r="B30" t="s">
-        <v>49</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>137</v>
+        <v>50</v>
       </c>
       <c r="B32" t="s">
-        <v>158</v>
+        <v>51</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>159</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>138</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>159</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B35" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>26</v>
+        <v>184</v>
       </c>
       <c r="B36" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>184</v>
+        <v>34</v>
       </c>
       <c r="B37" t="s">
-        <v>185</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B39" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>197</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>198</v>
+        <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
         <v>196</v>
@@ -1396,481 +1400,457 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="1" t="s">
-        <v>4</v>
+        <v>142</v>
       </c>
       <c r="B43" t="s">
-        <v>196</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="1" t="s">
-        <v>142</v>
+        <v>108</v>
       </c>
       <c r="B44" t="s">
-        <v>161</v>
+        <v>199</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="1" t="s">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="B45" t="s">
-        <v>199</v>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="1" t="s">
-        <v>58</v>
+        <v>143</v>
       </c>
       <c r="B47" t="s">
-        <v>59</v>
+        <v>162</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="1" t="s">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="B48" t="s">
-        <v>162</v>
+        <v>185</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>184</v>
+        <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>185</v>
+        <v>67</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="B50" t="s">
-        <v>67</v>
+        <v>121</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B51" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="B52" t="s">
-        <v>115</v>
+        <v>55</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="B53" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>5</v>
+        <v>144</v>
       </c>
       <c r="B54" t="s">
-        <v>67</v>
+        <v>163</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B55" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>145</v>
+        <v>6</v>
       </c>
       <c r="B56" t="s">
-        <v>164</v>
+        <v>67</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>7</v>
+        <v>103</v>
       </c>
       <c r="B58" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="B59" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>107</v>
+        <v>61</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B62" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B63" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B64" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B65" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B66" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="1" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="B67" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="1" t="s">
-        <v>130</v>
+        <v>23</v>
       </c>
       <c r="B68" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="1" t="s">
-        <v>25</v>
+        <v>146</v>
       </c>
       <c r="B70" t="s">
-        <v>81</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B72" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="1" t="s">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="B73" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B74" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B75" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B76" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B77" t="s">
-        <v>78</v>
+        <v>186</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>188</v>
+        <v>21</v>
+      </c>
+      <c r="B78" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B79" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B80" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>77</v>
+        <v>126</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B83" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B84" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B85" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B86" t="s">
-        <v>74</v>
+        <v>187</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>189</v>
+        <v>13</v>
+      </c>
+      <c r="B87" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B88" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="1" t="s">
-        <v>11</v>
+        <v>151</v>
       </c>
       <c r="B89" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="1" t="s">
-        <v>151</v>
+        <v>62</v>
       </c>
       <c r="B90" t="s">
-        <v>170</v>
+        <v>66</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="1" t="s">
-        <v>132</v>
+        <v>64</v>
       </c>
       <c r="B91" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="1" t="s">
-        <v>152</v>
+        <v>2</v>
       </c>
       <c r="B92" t="s">
-        <v>171</v>
+        <v>33</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B93" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="94" spans="1:2">
-      <c r="A94" s="1" t="s">
-        <v>64</v>
+      <c r="A94" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="B94" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="95" spans="1:2">
-      <c r="A95" s="1" t="s">
-        <v>2</v>
+      <c r="A95" t="s">
+        <v>172</v>
       </c>
       <c r="B95" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="96" spans="1:2">
-      <c r="A96" s="1" t="s">
-        <v>63</v>
+      <c r="A96" s="5" t="s">
+        <v>173</v>
       </c>
       <c r="B96" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="97" spans="1:2">
-      <c r="A97" s="1" t="s">
-        <v>155</v>
+      <c r="A97" t="s">
+        <v>190</v>
       </c>
       <c r="B97" t="s">
-        <v>36</v>
+        <v>191</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="B98" t="s">
-        <v>37</v>
+        <v>194</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="B99" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" t="s">
-        <v>190</v>
-      </c>
-      <c r="B100" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" t="s">
-        <v>192</v>
-      </c>
-      <c r="B101" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" t="s">
-        <v>193</v>
-      </c>
-      <c r="B102" t="s">
         <v>195</v>
       </c>
     </row>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C27339A-679B-4FC3-92AB-EA1ADCC2F12E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E67BC6-2D88-4AD2-ABB8-D58DA6751652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
   <sheets>
     <sheet name="SimpleLeafRenames" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="200">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -705,7 +705,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -716,10 +716,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1055,11 +1051,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
-  <dimension ref="A1:B99"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:B100"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="56.109375" customWidth="1"/>
-    <col min="2" max="2" width="87.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56.140625" customWidth="1"/>
+    <col min="2" max="2" width="87.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1768,89 +1764,97 @@
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="1" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="B89" t="s">
-        <v>170</v>
+        <v>59</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="1" t="s">
-        <v>62</v>
+        <v>151</v>
       </c>
       <c r="B90" t="s">
-        <v>66</v>
+        <v>170</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B91" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="1" t="s">
-        <v>2</v>
+        <v>64</v>
       </c>
       <c r="B92" t="s">
-        <v>33</v>
+        <v>64</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B93" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B94" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
-      <c r="A94" s="6" t="s">
+    <row r="95" spans="1:2">
+      <c r="A95" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B95" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
-      <c r="A95" t="s">
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
         <v>172</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B96" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B96" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="B97" t="s">
-        <v>191</v>
+        <v>36</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B98" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
+        <v>192</v>
+      </c>
+      <c r="B99" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
         <v>193</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B100" t="s">
         <v>195</v>
       </c>
     </row>
@@ -1862,7 +1866,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B7E1F01-A2F7-45A9-995C-5EC6E55D65FA}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -1896,10 +1900,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F34CFB7-6746-4EED-A01C-0BEF089865E6}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.109375" customWidth="1"/>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1998,7 +2002,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C94458-8D2F-45A6-90CE-3561672AE312}">
   <dimension ref="A1:B89"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="79" bestFit="1" customWidth="1"/>
   </cols>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1E67BC6-2D88-4AD2-ABB8-D58DA6751652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD7669C-5902-44EF-A3FF-E6B865C9BD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
+    <workbookView xWindow="-16320" yWindow="-5925" windowWidth="16440" windowHeight="28320" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
   <sheets>
     <sheet name="SimpleLeafRenames" sheetId="1" r:id="rId1"/>
@@ -611,9 +611,6 @@
     <t>Wheat.Stem.Live.Weight.Storage</t>
   </si>
   <si>
-    <t>(Wheat.Leaf.Transpiration+ISoilWater.Es+MicroClimate.PrecipitationInterception)</t>
-  </si>
-  <si>
     <t>(Wheat.Leaf.Transpiration + ISoilWater.Es + MicroClimate.PrecipitationInterception)</t>
   </si>
   <si>
@@ -639,6 +636,9 @@
   </si>
   <si>
     <t>Wheat.Leaf.Canopy.GreenSpecificNitrogen</t>
+  </si>
+  <si>
+    <t>(Wheat.Leaf.Canopy.Transpiration + ISoilWater.Es + MicroClimate.PrecipitationInterception)</t>
   </si>
 </sst>
 </file>
@@ -1054,7 +1054,7 @@
   <dimension ref="A1:B100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="56.140625" customWidth="1"/>
+    <col min="1" max="1" width="71.42578125" customWidth="1"/>
     <col min="2" max="2" width="87.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1372,10 +1372,10 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B40" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>52</v>
       </c>
       <c r="B41" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>4</v>
       </c>
       <c r="B42" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>108</v>
       </c>
       <c r="B44" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1839,23 +1839,23 @@
         <v>190</v>
       </c>
       <c r="B98" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B99" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B100" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -1878,18 +1878,18 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BD7669C-5902-44EF-A3FF-E6B865C9BD8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8827BCB0-4979-4923-A059-BB6DB6DCB541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-5925" windowWidth="16440" windowHeight="28320" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="261">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -639,6 +639,189 @@
   </si>
   <si>
     <t>(Wheat.Leaf.Canopy.Transpiration + ISoilWater.Es + MicroClimate.PrecipitationInterception)</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.TerminalSpikeletDAS</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.FlagLeafDAS</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.HeadingDAS</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.HarvestRipeDAS</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.MaximumSpikeletPrimordiaDAS</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.FlagLeafAppearanceDAS</t>
+  </si>
+  <si>
+    <t>Wheat.Phenology.HeadEmergenceDAS</t>
+  </si>
+  <si>
+    <t>DoubleRidge</t>
+  </si>
+  <si>
+    <t>[Phenology].HaunStage</t>
+  </si>
+  <si>
+    <t>[Leaf].HaunStage</t>
+  </si>
+  <si>
+    <t>[Leaf].ExpandedCohortNo</t>
+  </si>
+  <si>
+    <t>[Phenology].GrainDevelopment.Target</t>
+  </si>
+  <si>
+    <t>[Phenology].GrainExpanding.Target</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> [Phenology].Maturing.Target </t>
+  </si>
+  <si>
+    <t>[Phenology].Maturing.ProgressThroughPhase</t>
+  </si>
+  <si>
+    <t>[Phenology].GrainRipening.Target</t>
+  </si>
+  <si>
+    <t>[Phenology].GrainRipening.ProgressThroughPhase</t>
+  </si>
+  <si>
+    <t>VernalSaturation</t>
+  </si>
+  <si>
+    <t>Vernalising</t>
+  </si>
+  <si>
+    <t>LeavesInitiating</t>
+  </si>
+  <si>
+    <t>TerminalSpikelet</t>
+  </si>
+  <si>
+    <t>MaximumSpikeletPrimordia</t>
+  </si>
+  <si>
+    <t>SpikeletDifferentiation</t>
+  </si>
+  <si>
+    <t>SpikeletsDifferentiating</t>
+  </si>
+  <si>
+    <t>StemElongation</t>
+  </si>
+  <si>
+    <t>StemElongating</t>
+  </si>
+  <si>
+    <t>"FlagLeaf"</t>
+  </si>
+  <si>
+    <t>"FlagLeafAppearance"</t>
+  </si>
+  <si>
+    <t>Heading</t>
+  </si>
+  <si>
+    <t>HeadEmergence</t>
+  </si>
+  <si>
+    <t>Flowering</t>
+  </si>
+  <si>
+    <t>Anthesis</t>
+  </si>
+  <si>
+    <t>EarlyFlowering</t>
+  </si>
+  <si>
+    <t>StartGrainFill</t>
+  </si>
+  <si>
+    <t>MaximumGrainLength</t>
+  </si>
+  <si>
+    <t>GrainDevelopment</t>
+  </si>
+  <si>
+    <t>GrainExpanding</t>
+  </si>
+  <si>
+    <t>Ripening</t>
+  </si>
+  <si>
+    <t>GrainRipening</t>
+  </si>
+  <si>
+    <t>Maturity</t>
+  </si>
+  <si>
+    <t>HarvestRipe</t>
+  </si>
+  <si>
+    <t>[Stem].DMRetranslocationFactor.ReproductiveGrowth.DMRetranslocationFactor.FixedValue</t>
+  </si>
+  <si>
+    <t>[Leaf].CohortParameters.MaxArea.AreaLargestLeaves.FixedValue</t>
+  </si>
+  <si>
+    <t>[Leaf].ExtinctionCoeff.VegetativePhase.FixedValue</t>
+  </si>
+  <si>
+    <t>[Structure].BranchingRate.PotentialBranchingRate.Vegetative.PotentialBranchingRate.XYPairs.Y</t>
+  </si>
+  <si>
+    <t>[Grain].MaximumNConc.FixedValue</t>
+  </si>
+  <si>
+    <t>[Grain].MaxNConcDailyGrowth.FixedValue</t>
+  </si>
+  <si>
+    <t>[Leaf].ExtinctionCoeff.DevelopmentFactor.XYPairs.Y</t>
+  </si>
+  <si>
+    <t>[Leaf].CohortParameters.MinimumNConc.XYPairs.Y</t>
+  </si>
+  <si>
+    <t>[Stem].MinimumNConc.FixedValue</t>
+  </si>
+  <si>
+    <t>[Spike].DMRetranslocationFactor.ReproductiveGrowth.DMRetranslocationFactor.FixedValue</t>
+  </si>
+  <si>
+    <t>//[Stem].DMRetranslocationFactor.ReproductiveGrowth.DMRetranslocationFactor.FixedValue</t>
+  </si>
+  <si>
+    <t>//[Leaf].AreaOfLargest.FixedValue</t>
+  </si>
+  <si>
+    <t>[Leaf].Canopy.GreenExtinctionCoeff.VegetativePhase.FixedValue</t>
+  </si>
+  <si>
+    <t>//[Structure].BranchingRate.PotentialBranchingRate.Vegetative.PotentialBranchingRate.XYPairs.Y</t>
+  </si>
+  <si>
+    <t>//[Grain].MaximumNConc.FixedValue</t>
+  </si>
+  <si>
+    <t>//[Grain].MaxNConcDailyGrowth.FixedValue</t>
+  </si>
+  <si>
+    <t>//[Leaf].ExtinctionCoeff.DevelopmentFactor.XYPairs.Y</t>
+  </si>
+  <si>
+    <t>//[Leaf].CohortParameters.MinimumNConc.XYPairs.Y</t>
+  </si>
+  <si>
+    <t>//[Stem].MinimumNConc.FixedValue</t>
+  </si>
+  <si>
+    <t>//[Spike].DMRetranslocationFactor.ReproductiveGrowth.DMRetranslocationFactor.FixedValue</t>
   </si>
 </sst>
 </file>
@@ -705,7 +888,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -717,6 +900,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1051,7 +1235,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
-  <dimension ref="A1:B100"/>
+  <dimension ref="A1:B134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="71.42578125" customWidth="1"/>
@@ -1856,6 +2040,278 @@
       </c>
       <c r="B100" t="s">
         <v>194</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>200</v>
+      </c>
+      <c r="B101" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
+        <v>201</v>
+      </c>
+      <c r="B102" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>202</v>
+      </c>
+      <c r="B103" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>175</v>
+      </c>
+      <c r="B104" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" t="s">
+        <v>177</v>
+      </c>
+      <c r="B105" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>2</v>
+      </c>
+      <c r="B106" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>208</v>
+      </c>
+      <c r="B107" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>210</v>
+      </c>
+      <c r="B108" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>211</v>
+      </c>
+      <c r="B109" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>213</v>
+      </c>
+      <c r="B110" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>214</v>
+      </c>
+      <c r="B111" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>217</v>
+      </c>
+      <c r="B112" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" t="s">
+        <v>218</v>
+      </c>
+      <c r="B113" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>220</v>
+      </c>
+      <c r="B114" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" t="s">
+        <v>222</v>
+      </c>
+      <c r="B115" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" t="s">
+        <v>224</v>
+      </c>
+      <c r="B116" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" t="s">
+        <v>228</v>
+      </c>
+      <c r="B118" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" t="s">
+        <v>230</v>
+      </c>
+      <c r="B119" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>232</v>
+      </c>
+      <c r="B120" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>233</v>
+      </c>
+      <c r="B121" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>235</v>
+      </c>
+      <c r="B122" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>237</v>
+      </c>
+      <c r="B123" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>239</v>
+      </c>
+      <c r="B124" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" t="s">
+        <v>241</v>
+      </c>
+      <c r="B125" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
+        <v>242</v>
+      </c>
+      <c r="B126" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
+        <v>243</v>
+      </c>
+      <c r="B127" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
+        <v>244</v>
+      </c>
+      <c r="B128" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>245</v>
+      </c>
+      <c r="B129" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" t="s">
+        <v>246</v>
+      </c>
+      <c r="B130" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>247</v>
+      </c>
+      <c r="B131" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>248</v>
+      </c>
+      <c r="B132" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>249</v>
+      </c>
+      <c r="B133" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
+        <v>250</v>
+      </c>
+      <c r="B134" t="s">
+        <v>260</v>
       </c>
     </row>
   </sheetData>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8827BCB0-4979-4923-A059-BB6DB6DCB541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C24F85-0008-4526-9B26-520259A9B076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-16320" yWindow="-5925" windowWidth="16440" windowHeight="28320" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="263">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -800,9 +800,6 @@
     <t>//[Leaf].AreaOfLargest.FixedValue</t>
   </si>
   <si>
-    <t>[Leaf].Canopy.GreenExtinctionCoeff.VegetativePhase.FixedValue</t>
-  </si>
-  <si>
     <t>//[Structure].BranchingRate.PotentialBranchingRate.Vegetative.PotentialBranchingRate.XYPairs.Y</t>
   </si>
   <si>
@@ -822,6 +819,15 @@
   </si>
   <si>
     <t>//[Spike].DMRetranslocationFactor.ReproductiveGrowth.DMRetranslocationFactor.FixedValue</t>
+  </si>
+  <si>
+    <t>[Stem].DMDemands.Structural.StructuralFraction.VegetativeGrowth.Fraction.FixedValue</t>
+  </si>
+  <si>
+    <t>//[Stem].DMDemands.Structural.StructuralFraction.VegetativeGrowth.Fraction.FixedValue</t>
+  </si>
+  <si>
+    <t>[Leaf].Canopy.GreenExtinctionCoefficient.VegetativePhase.FixedValue</t>
   </si>
 </sst>
 </file>
@@ -1235,7 +1241,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
-  <dimension ref="A1:B134"/>
+  <dimension ref="A1:B135"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="71.42578125" customWidth="1"/>
@@ -2255,7 +2261,7 @@
         <v>243</v>
       </c>
       <c r="B127" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -2263,7 +2269,7 @@
         <v>244</v>
       </c>
       <c r="B128" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -2271,7 +2277,7 @@
         <v>245</v>
       </c>
       <c r="B129" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -2279,7 +2285,7 @@
         <v>246</v>
       </c>
       <c r="B130" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -2287,7 +2293,7 @@
         <v>247</v>
       </c>
       <c r="B131" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -2295,7 +2301,7 @@
         <v>248</v>
       </c>
       <c r="B132" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -2303,7 +2309,7 @@
         <v>249</v>
       </c>
       <c r="B133" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -2311,7 +2317,15 @@
         <v>250</v>
       </c>
       <c r="B134" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
         <v>260</v>
+      </c>
+      <c r="B135" t="s">
+        <v>261</v>
       </c>
     </row>
   </sheetData>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22C24F85-0008-4526-9B26-520259A9B076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B207AD70-6638-42AA-86E5-C25CFA3727BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-5925" windowWidth="16440" windowHeight="28320" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
   <sheets>
     <sheet name="SimpleLeafRenames" sheetId="1" r:id="rId1"/>
@@ -752,12 +752,6 @@
     <t>GrainExpanding</t>
   </si>
   <si>
-    <t>Ripening</t>
-  </si>
-  <si>
-    <t>GrainRipening</t>
-  </si>
-  <si>
     <t>Maturity</t>
   </si>
   <si>
@@ -828,6 +822,12 @@
   </si>
   <si>
     <t>[Leaf].Canopy.GreenExtinctionCoefficient.VegetativePhase.FixedValue</t>
+  </si>
+  <si>
+    <t>"Ripening"</t>
+  </si>
+  <si>
+    <t>"GrainRipening'"</t>
   </si>
 </sst>
 </file>
@@ -1242,10 +1242,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
   <dimension ref="A1:B135"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="71.42578125" customWidth="1"/>
-    <col min="2" max="2" width="87.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="71.44140625" customWidth="1"/>
+    <col min="2" max="2" width="87.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2225,107 +2225,107 @@
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" t="s">
-        <v>237</v>
-      </c>
-      <c r="B123" t="s">
-        <v>238</v>
+      <c r="A123" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B124" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B125" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B126" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B127" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B128" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B129" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B130" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B131" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B132" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B133" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B134" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B135" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -2336,7 +2336,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B7E1F01-A2F7-45A9-995C-5EC6E55D65FA}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -2370,10 +2370,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F34CFB7-6746-4EED-A01C-0BEF089865E6}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="48.140625" customWidth="1"/>
-    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.109375" customWidth="1"/>
+    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2472,7 +2472,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C94458-8D2F-45A6-90CE-3561672AE312}">
   <dimension ref="A1:B89"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="79" bestFit="1" customWidth="1"/>
   </cols>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B207AD70-6638-42AA-86E5-C25CFA3727BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366A87A5-D241-467F-AD07-709D184664B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="265">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -828,6 +828,12 @@
   </si>
   <si>
     <t>"GrainRipening'"</t>
+  </si>
+  <si>
+    <t>"MaxLeafSize"</t>
+  </si>
+  <si>
+    <t>"OutputMaxLeafSize"</t>
   </si>
 </sst>
 </file>
@@ -1241,7 +1247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
-  <dimension ref="A1:B135"/>
+  <dimension ref="A1:B136"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="71.44140625" customWidth="1"/>
@@ -2034,297 +2040,305 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>191</v>
+        <v>263</v>
       </c>
       <c r="B99" t="s">
-        <v>193</v>
+        <v>264</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B100" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="B101" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B102" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B103" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="B104" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B105" t="s">
-        <v>203</v>
+        <v>174</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>2</v>
+        <v>177</v>
       </c>
       <c r="B106" t="s">
-        <v>33</v>
+        <v>203</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>208</v>
+        <v>2</v>
       </c>
       <c r="B107" t="s">
-        <v>209</v>
+        <v>33</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B108" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B109" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B110" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B111" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B112" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B113" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B114" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B115" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
+        <v>222</v>
+      </c>
+      <c r="B116" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" t="s">
         <v>224</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B117" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
-      <c r="A117" s="5" t="s">
+    <row r="118" spans="1:2">
+      <c r="A118" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B117" s="5" t="s">
+      <c r="B118" s="5" t="s">
         <v>227</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" t="s">
-        <v>228</v>
-      </c>
-      <c r="B118" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B119" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B120" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B121" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
+        <v>233</v>
+      </c>
+      <c r="B122" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
         <v>235</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B123" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
-      <c r="A123" s="5" t="s">
+    <row r="124" spans="1:2">
+      <c r="A124" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="B123" s="5" t="s">
+      <c r="B124" s="5" t="s">
         <v>262</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124" t="s">
-        <v>237</v>
-      </c>
-      <c r="B124" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B125" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B126" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B127" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B128" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B129" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B130" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B131" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B132" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B133" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B134" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
+        <v>248</v>
+      </c>
+      <c r="B135" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
         <v>258</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B136" t="s">
         <v>259</v>
       </c>
     </row>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366A87A5-D241-467F-AD07-709D184664B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FB1C79-D6D1-4631-8F12-D8780C8B570D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="269">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -830,10 +830,22 @@
     <t>"GrainRipening'"</t>
   </si>
   <si>
-    <t>"MaxLeafSize"</t>
-  </si>
-  <si>
-    <t>"OutputMaxLeafSize"</t>
+    <t>[MaxLeafSize].Script</t>
+  </si>
+  <si>
+    <t>[OutputMaxLeafSize].Script</t>
+  </si>
+  <si>
+    <t>ReportLeafSize</t>
+  </si>
+  <si>
+    <t>LeafReport</t>
+  </si>
+  <si>
+    <t>[OutputMaxLeafSize].Script.LeafSize</t>
+  </si>
+  <si>
+    <t>//[OutputMaxLeafSize].Script.LeafSize</t>
   </si>
 </sst>
 </file>
@@ -1247,7 +1259,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
-  <dimension ref="A1:B136"/>
+  <dimension ref="A1:B138"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="71.44140625" customWidth="1"/>
@@ -2064,281 +2076,297 @@
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>200</v>
+        <v>266</v>
       </c>
       <c r="B102" t="s">
-        <v>204</v>
+        <v>265</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="B103" t="s">
-        <v>205</v>
+        <v>268</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B104" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>175</v>
+        <v>201</v>
       </c>
       <c r="B105" t="s">
-        <v>174</v>
+        <v>205</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" t="s">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="B106" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>2</v>
+        <v>175</v>
       </c>
       <c r="B107" t="s">
-        <v>33</v>
+        <v>174</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="B108" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>210</v>
+        <v>2</v>
       </c>
       <c r="B109" t="s">
-        <v>210</v>
+        <v>33</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B110" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B111" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B112" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B113" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B114" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B115" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B116" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B117" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="118" spans="1:2">
-      <c r="A118" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>227</v>
+      <c r="A118" t="s">
+        <v>222</v>
+      </c>
+      <c r="B118" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B119" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
     </row>
     <row r="120" spans="1:2">
-      <c r="A120" t="s">
-        <v>230</v>
-      </c>
-      <c r="B120" t="s">
-        <v>231</v>
+      <c r="A120" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B121" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B122" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B123" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="124" spans="1:2">
-      <c r="A124" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>262</v>
+      <c r="A124" t="s">
+        <v>233</v>
+      </c>
+      <c r="B124" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B125" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="126" spans="1:2">
-      <c r="A126" t="s">
-        <v>239</v>
-      </c>
-      <c r="B126" t="s">
-        <v>249</v>
+      <c r="A126" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B127" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B128" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B129" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B130" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B131" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B132" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B133" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B134" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B135" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
+        <v>247</v>
+      </c>
+      <c r="B136" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>248</v>
+      </c>
+      <c r="B137" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
         <v>258</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B138" t="s">
         <v>259</v>
       </c>
     </row>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FB1C79-D6D1-4631-8F12-D8780C8B570D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0F39ED-5A28-479D-8B3C-CDB4C1CDC6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="270">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -846,6 +846,9 @@
   </si>
   <si>
     <t>//[OutputMaxLeafSize].Script.LeafSize</t>
+  </si>
+  <si>
+    <t>//[Leaf].Canopy.GreenExtinctionCoefficient.VegetativePhase.FixedValue</t>
   </si>
 </sst>
 </file>
@@ -1259,7 +1262,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
-  <dimension ref="A1:B138"/>
+  <dimension ref="A1:B139"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="71.44140625" customWidth="1"/>
@@ -2308,65 +2311,73 @@
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B131" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B132" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B133" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B134" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B135" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B136" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B137" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
+        <v>248</v>
+      </c>
+      <c r="B138" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
         <v>258</v>
       </c>
-      <c r="B138" t="s">
+      <c r="B139" t="s">
         <v>259</v>
       </c>
     </row>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F0F39ED-5A28-479D-8B3C-CDB4C1CDC6A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC1A3A7-48FF-40C0-8F28-95554994F233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
   <sheets>
     <sheet name="SimpleLeafRenames" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="276">
   <si>
     <t>CohortLeaf</t>
   </si>
@@ -849,6 +849,24 @@
   </si>
   <si>
     <t>//[Leaf].Canopy.GreenExtinctionCoefficient.VegetativePhase.FixedValue</t>
+  </si>
+  <si>
+    <t>[Wheat].Phenology.Phyllochron.BasePhyllochron.FixedValue</t>
+  </si>
+  <si>
+    <t>[Wheat].Phenology.PhyllochronPpSensitivity.FixedValue</t>
+  </si>
+  <si>
+    <t>[Wheat].Leaf.Phyllochron.BasePhyllochron.FixedValue</t>
+  </si>
+  <si>
+    <t>[Wheat].Leaf.PhyllochronPpSensitivity.FixedValue</t>
+  </si>
+  <si>
+    <t>Name: "Flowering"</t>
+  </si>
+  <si>
+    <t>Name: "Anthesis"</t>
   </si>
 </sst>
 </file>
@@ -1262,11 +1280,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45DFA9DE-B569-4853-98A7-0B05A40C5DD2}">
-  <dimension ref="A1:B139"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:B142"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="71.44140625" customWidth="1"/>
-    <col min="2" max="2" width="87.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="71.42578125" customWidth="1"/>
+    <col min="2" max="2" width="87.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2247,138 +2265,162 @@
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>232</v>
+        <v>275</v>
       </c>
       <c r="B123" t="s">
-        <v>230</v>
+        <v>274</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B124" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
+        <v>233</v>
+      </c>
+      <c r="B125" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
         <v>235</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B126" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
-      <c r="A126" s="5" t="s">
+    <row r="127" spans="1:2">
+      <c r="A127" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="B126" s="5" t="s">
+      <c r="B127" s="5" t="s">
         <v>262</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" t="s">
-        <v>237</v>
-      </c>
-      <c r="B127" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B128" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B129" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B130" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
+        <v>241</v>
+      </c>
+      <c r="B131" t="s">
         <v>260</v>
-      </c>
-      <c r="B131" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B132" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B133" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B134" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B135" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B136" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B137" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B138" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
+        <v>248</v>
+      </c>
+      <c r="B139" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
         <v>258</v>
       </c>
-      <c r="B139" t="s">
+      <c r="B140" t="s">
         <v>259</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>270</v>
+      </c>
+      <c r="B141" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>271</v>
+      </c>
+      <c r="B142" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -2389,7 +2431,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B7E1F01-A2F7-45A9-995C-5EC6E55D65FA}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
@@ -2423,10 +2465,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F34CFB7-6746-4EED-A01C-0BEF089865E6}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48.109375" customWidth="1"/>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="48.140625" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -2525,7 +2567,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C94458-8D2F-45A6-90CE-3561672AE312}">
   <dimension ref="A1:B89"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="79" bestFit="1" customWidth="1"/>
   </cols>

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AC1A3A7-48FF-40C0-8F28-95554994F233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1137727B-32EB-4DFB-8C0B-1CCD0D43D9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
@@ -2332,7 +2332,7 @@
         <v>241</v>
       </c>
       <c r="B131" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
     </row>
     <row r="132" spans="1:2">

--- a/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
+++ b/Prototypes/WheatSimpleLeaf/SimpleLeafImplementation/VariableRenames.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHubRepos\ApsimX\Prototypes\WheatSimpleLeaf\SimpleLeafImplementation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1137727B-32EB-4DFB-8C0B-1CCD0D43D9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E154799-D134-4D7A-A3C8-6DEB813EB1B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{99730FEE-4914-42B9-ACDB-525A29E01521}"/>
   </bookViews>
@@ -863,10 +863,10 @@
     <t>[Wheat].Leaf.PhyllochronPpSensitivity.FixedValue</t>
   </si>
   <si>
-    <t>Name: "Flowering"</t>
-  </si>
-  <si>
-    <t>Name: "Anthesis"</t>
+    <t>"Name": "Anthesis",</t>
+  </si>
+  <si>
+    <t>"Name": "Flowering",</t>
   </si>
 </sst>
 </file>
@@ -2264,11 +2264,11 @@
       </c>
     </row>
     <row r="123" spans="1:2">
-      <c r="A123" t="s">
+      <c r="A123" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="B123" s="5" t="s">
         <v>275</v>
-      </c>
-      <c r="B123" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="124" spans="1:2">
